--- a/static/contracts/items_write_test.xlsx
+++ b/static/contracts/items_write_test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14916" yWindow="732" windowWidth="8124" windowHeight="11508" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>供方A</t>
         </is>
       </c>
       <c r="M3" s="12" t="n"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="V3" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>HT-T</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>需方B</t>
         </is>
       </c>
       <c r="M4" s="12" t="n"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-001</t>
         </is>
       </c>
     </row>
@@ -1047,52 +1047,36 @@
       <c r="AG7" s="25" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" s="17" t="n">
-        <v>1</v>
-      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="26" t="n"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="D8" s="17" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="26" t="n"/>
       <c r="H8" s="17" t="n"/>
       <c r="I8" s="26" t="n"/>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
+      <c r="J8" s="18" t="n"/>
       <c r="K8" s="26" t="n"/>
       <c r="L8" s="27" t="n"/>
       <c r="M8" s="18" t="inlineStr">
         <is>
-          <t>MC1</t>
+          <t>（附清单）</t>
         </is>
       </c>
       <c r="N8" s="26" t="n"/>
       <c r="O8" s="27" t="n"/>
-      <c r="P8" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="P8" s="17" t="n"/>
       <c r="Q8" s="26" t="n"/>
       <c r="R8" s="18" t="n"/>
       <c r="S8" s="27" t="n"/>
-      <c r="T8" s="18" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="T8" s="18" t="n"/>
       <c r="U8" s="27" t="n"/>
       <c r="V8" s="18" t="n"/>
       <c r="W8" s="27" t="n"/>
       <c r="X8" s="17" t="n"/>
       <c r="Y8" s="26" t="n"/>
       <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="17" t="n">
-        <v>7</v>
-      </c>
+      <c r="AA8" s="17" t="n"/>
       <c r="AB8" s="17" t="n"/>
       <c r="AC8" s="26" t="n"/>
       <c r="AD8" s="18" t="n"/>
@@ -1103,28 +1087,33 @@
     <row r="9" ht="24" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>合计人民币金额(大写):</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>贰拾柒圆整</t>
+          <t>柒圆整</t>
         </is>
       </c>
       <c r="P9" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="T9" s="12" t="n"/>
       <c r="V9" s="12" t="n"/>
       <c r="X9" s="12" t="n"/>
       <c r="AA9" s="20" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="0.75" customHeight="1">
-      <c r="B10" s="21" t="inlineStr"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>采
+购
+条
+款</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1">
@@ -1222,7 +1211,6 @@
       </c>
     </row>
     <row r="26" ht="16.05" customHeight="1">
-      <c r="C26" t="inlineStr"/>
       <c r="D26" s="12" t="inlineStr">
         <is>
           <t>供方</t>
@@ -1256,7 +1244,7 @@
     <row r="27" ht="16.05" customHeight="1">
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>地址：</t>
+          <t>地址1</t>
         </is>
       </c>
       <c r="I27" s="9" t="n"/>
@@ -1276,7 +1264,7 @@
     <row r="28" ht="16.05" customHeight="1">
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>法定代理人：</t>
+          <t>法人1</t>
         </is>
       </c>
       <c r="I28" s="9" t="n"/>
@@ -1296,7 +1284,7 @@
     <row r="29" ht="16.05" customHeight="1">
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>委托代理人：</t>
+          <t>代理1</t>
         </is>
       </c>
       <c r="I29" s="9" t="n"/>
@@ -1316,7 +1304,7 @@
     <row r="30" ht="16.05" customHeight="1">
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>联系电话：</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I30" s="9" t="n"/>
@@ -1332,7 +1320,7 @@
     <row r="31" ht="16.05" customHeight="1">
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>开户银行：</t>
+          <t>工行</t>
         </is>
       </c>
       <c r="I31" s="9" t="n"/>
@@ -1352,7 +1340,7 @@
     <row r="32" ht="16.05" customHeight="1">
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>账号：</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="I32" s="9" t="n"/>
@@ -1372,7 +1360,7 @@
     <row r="33" ht="16.05" customHeight="1">
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>税号：</t>
+          <t>TAX1</t>
         </is>
       </c>
       <c r="I33" s="9" t="n"/>
@@ -1574,35 +1562,51 @@
       <c r="AG41" s="25" t="n"/>
     </row>
     <row r="42" ht="57.75" customHeight="1">
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n"/>
+      <c r="B42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
       <c r="D42" s="24" t="n"/>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="25" t="n"/>
-      <c r="G42" s="14" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>阀门</t>
+        </is>
+      </c>
       <c r="H42" s="25" t="n"/>
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="25" t="n"/>
-      <c r="K42" s="14" t="n"/>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>VM-01</t>
+        </is>
+      </c>
       <c r="L42" s="24" t="n"/>
       <c r="M42" s="24" t="n"/>
       <c r="N42" s="25" t="n"/>
-      <c r="O42" s="14" t="n"/>
+      <c r="O42" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="P42" s="25" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="25" t="n"/>
-      <c r="S42" s="14" t="n"/>
+      <c r="S42" s="14" t="n">
+        <v>3.5</v>
+      </c>
       <c r="T42" s="25" t="n"/>
       <c r="U42" s="14" t="n"/>
       <c r="V42" s="25" t="n"/>
       <c r="W42" s="14" t="n"/>
       <c r="X42" s="24" t="n"/>
       <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="14" t="n"/>
+      <c r="Z42" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="AA42" s="24" t="n"/>
       <c r="AB42" s="25" t="n"/>
       <c r="AC42" s="14" t="n"/>
